--- a/Docs/ISO_Controls/ISO27001_Control_Framework_MasterDoc_18Dec2025.xlsx
+++ b/Docs/ISO_Controls/ISO27001_Control_Framework_MasterDoc_18Dec2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Allison\Documents\SFU\IntelliAudit\ISO_Controls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allyftw\Documents\GitHub\IntelliAudit\Docs\ISO_Controls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E18015-0503-495F-906A-3B7F1A0E4533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D966EDEA-F760-4352-9BCD-222B5C91382B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="15090" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control Overview" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="483">
   <si>
     <t>Control ID</t>
   </si>
@@ -1383,12 +1383,6 @@
     <t>Diagram</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Complete</t>
-  </si>
-  <si>
     <t>Org Chart (PDF)</t>
   </si>
   <si>
@@ -1458,9 +1452,6 @@
     <t>5.x controls; Access controls; Secure Development Life Cycle (8.25)</t>
   </si>
   <si>
-    <t>Partial Completion, TBD January</t>
-  </si>
-  <si>
     <t>Compliant</t>
   </si>
   <si>
@@ -1477,6 +1468,12 @@
   </si>
   <si>
     <t>The organization has no history of meeting nor attempting to the meet the control.</t>
+  </si>
+  <si>
+    <t>Data Generated</t>
+  </si>
+  <si>
+    <t>Data Generated, Dev Build Completed</t>
   </si>
 </sst>
 </file>
@@ -2289,7 +2286,7 @@
         <v>315</v>
       </c>
       <c r="H16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3450,7 +3447,7 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F61" t="s">
         <v>151</v>
@@ -3476,7 +3473,7 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F62" t="s">
         <v>154</v>
@@ -3502,7 +3499,7 @@
         <v>55</v>
       </c>
       <c r="E63" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F63" t="s">
         <v>374</v>
@@ -3528,7 +3525,7 @@
         <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F64" t="s">
         <v>375</v>
@@ -3554,7 +3551,7 @@
         <v>64</v>
       </c>
       <c r="E65" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F65" t="s">
         <v>376</v>
@@ -3580,7 +3577,7 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F66" t="s">
         <v>377</v>
@@ -3606,7 +3603,7 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F67" t="s">
         <v>165</v>
@@ -3632,7 +3629,7 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F68" t="s">
         <v>378</v>
@@ -3658,7 +3655,7 @@
         <v>41</v>
       </c>
       <c r="E69" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F69" t="s">
         <v>379</v>
@@ -3684,7 +3681,7 @@
         <v>55</v>
       </c>
       <c r="E70" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F70" t="s">
         <v>380</v>
@@ -3710,7 +3707,7 @@
         <v>21</v>
       </c>
       <c r="E71" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F71" t="s">
         <v>381</v>
@@ -3736,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F72" t="s">
         <v>382</v>
@@ -3762,7 +3759,7 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F73" t="s">
         <v>383</v>
@@ -3788,7 +3785,7 @@
         <v>55</v>
       </c>
       <c r="E74" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F74" t="s">
         <v>384</v>
@@ -3814,7 +3811,7 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F75" t="s">
         <v>385</v>
@@ -3840,7 +3837,7 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F76" t="s">
         <v>404</v>
@@ -3866,7 +3863,7 @@
         <v>21</v>
       </c>
       <c r="E77" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F77" t="s">
         <v>386</v>
@@ -3892,7 +3889,7 @@
         <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F78" t="s">
         <v>387</v>
@@ -3918,7 +3915,7 @@
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F79" t="s">
         <v>388</v>
@@ -3944,7 +3941,7 @@
         <v>55</v>
       </c>
       <c r="E80" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F80" t="s">
         <v>389</v>
@@ -3970,7 +3967,7 @@
         <v>41</v>
       </c>
       <c r="E81" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F81" t="s">
         <v>390</v>
@@ -3996,7 +3993,7 @@
         <v>55</v>
       </c>
       <c r="E82" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F82" t="s">
         <v>391</v>
@@ -4022,7 +4019,7 @@
         <v>55</v>
       </c>
       <c r="E83" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F83" t="s">
         <v>198</v>
@@ -4048,7 +4045,7 @@
         <v>41</v>
       </c>
       <c r="E84" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F84" t="s">
         <v>392</v>
@@ -4074,7 +4071,7 @@
         <v>55</v>
       </c>
       <c r="E85" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F85" t="s">
         <v>203</v>
@@ -4100,7 +4097,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F86" t="s">
         <v>435</v>
@@ -4126,7 +4123,7 @@
         <v>41</v>
       </c>
       <c r="E87" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F87" t="s">
         <v>437</v>
@@ -4152,7 +4149,7 @@
         <v>55</v>
       </c>
       <c r="E88" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F88" t="s">
         <v>210</v>
@@ -4178,7 +4175,7 @@
         <v>55</v>
       </c>
       <c r="E89" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F89" t="s">
         <v>213</v>
@@ -4204,7 +4201,7 @@
         <v>41</v>
       </c>
       <c r="E90" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F90" t="s">
         <v>393</v>
@@ -4230,7 +4227,7 @@
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F91" t="s">
         <v>218</v>
@@ -4256,7 +4253,7 @@
         <v>41</v>
       </c>
       <c r="E92" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F92" t="s">
         <v>394</v>
@@ -4282,7 +4279,7 @@
         <v>41</v>
       </c>
       <c r="E93" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F93" t="s">
         <v>444</v>
@@ -4308,7 +4305,7 @@
         <v>55</v>
       </c>
       <c r="E94" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F94" t="s">
         <v>395</v>
@@ -4339,7 +4336,7 @@
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.85546875" customWidth="1"/>
     <col min="5" max="5" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.28515625" customWidth="1"/>
+    <col min="6" max="6" width="43.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4350,7 +4347,7 @@
         <v>448</v>
       </c>
       <c r="C1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D1" t="s">
         <v>449</v>
@@ -4359,7 +4356,7 @@
         <v>450</v>
       </c>
       <c r="F1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -4370,16 +4367,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D2" t="s">
         <v>450</v>
       </c>
       <c r="E2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F2" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4390,16 +4387,16 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D3" t="s">
         <v>451</v>
       </c>
       <c r="E3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F3" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4416,10 +4413,10 @@
         <v>450</v>
       </c>
       <c r="E4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F4" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4436,10 +4433,10 @@
         <v>450</v>
       </c>
       <c r="E5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F5" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4456,10 +4453,10 @@
         <v>450</v>
       </c>
       <c r="E6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F6" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4476,10 +4473,10 @@
         <v>450</v>
       </c>
       <c r="E7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F7" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4496,10 +4493,10 @@
         <v>450</v>
       </c>
       <c r="E8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F8" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4516,10 +4513,10 @@
         <v>450</v>
       </c>
       <c r="E9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F9" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4536,10 +4533,10 @@
         <v>450</v>
       </c>
       <c r="E10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F10" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4556,10 +4553,10 @@
         <v>450</v>
       </c>
       <c r="E11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F11" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4567,19 +4564,19 @@
         <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C12">
         <v>5.0999999999999996</v>
       </c>
       <c r="D12" t="s">
+        <v>466</v>
+      </c>
+      <c r="E12" t="s">
         <v>468</v>
       </c>
-      <c r="E12" t="s">
-        <v>470</v>
-      </c>
       <c r="F12" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4593,13 +4590,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D13" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4616,10 +4613,10 @@
         <v>450</v>
       </c>
       <c r="E14" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F14" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,13 +4630,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E15" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F15" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,13 +4650,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="D16" t="s">
+        <v>463</v>
+      </c>
+      <c r="E16" t="s">
         <v>465</v>
       </c>
-      <c r="E16" t="s">
-        <v>467</v>
-      </c>
       <c r="F16" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -15572,26 +15569,26 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
